--- a/YRIGOYEN 7630/Diciembre/YRIGOYEN7630-Diciembre.xlsx
+++ b/YRIGOYEN 7630/Diciembre/YRIGOYEN7630-Diciembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 7630\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF3D68B-CC6C-4CB4-A47F-DD5A872F16D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D03CD6-3AF5-4A24-93E9-35201377AAE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$120</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="115">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -139,9 +139,6 @@
     <t>Neto</t>
   </si>
   <si>
-    <t>Retenciones</t>
-  </si>
-  <si>
     <t>Total 2do Vto</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
   </si>
   <si>
     <t>ADMINISTRADORA: CAROLINA CANCIANI MP:1148</t>
-  </si>
-  <si>
-    <t>Retenciones SAC</t>
   </si>
   <si>
     <t>SAC</t>
@@ -326,51 +320,9 @@
     <t>Ascensores lema - Mantenimiento agosto</t>
   </si>
   <si>
-    <t xml:space="preserve">Fumigacion </t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Federacion patronal - Seguro de vida obligatorio Sr. Walter</t>
-  </si>
-  <si>
-    <t>Destapaciones italoamericana - Mantenimiento de cañertias, repaso a camaras de cloacas, ramales, salida a colectora. Mayo junio julio agosto septiembre</t>
-  </si>
-  <si>
-    <t>Transf 18/11</t>
-  </si>
-  <si>
-    <t>Transf 11/11</t>
-  </si>
-  <si>
-    <t>Debito 04/11</t>
-  </si>
-  <si>
-    <t>Debito 07/11</t>
-  </si>
-  <si>
-    <t>Debito 11/11</t>
-  </si>
-  <si>
-    <t>Debito 12/11</t>
-  </si>
-  <si>
-    <t>Debito 17/11</t>
-  </si>
-  <si>
-    <t>Pago parcial 18/11</t>
-  </si>
-  <si>
-    <t>Balcazza Leonardo - Adelanto terraza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kromacolor - Materiales </t>
-  </si>
-  <si>
-    <t>ACORDARSE DE QUE AL TOTAL ORDINARIOS LE SUMAMOS 400786</t>
-  </si>
-  <si>
     <t>VTO 15/01</t>
   </si>
   <si>
@@ -380,9 +332,6 @@
     <t>Gustavo padron - Sr contador honorarios DICIEMBRE</t>
   </si>
   <si>
-    <t>Honorarios administracion - Se debe DICIEMBRE</t>
-  </si>
-  <si>
     <t>Sindicatos mes de DICIEMBRE</t>
   </si>
   <si>
@@ -393,6 +342,36 @@
   </si>
   <si>
     <t>Transf 09/12</t>
+  </si>
+  <si>
+    <t>Debito 01/12</t>
+  </si>
+  <si>
+    <t>Debito 02/12</t>
+  </si>
+  <si>
+    <t>Debito 09/12</t>
+  </si>
+  <si>
+    <t>Debito 12/12</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Noviembre - Se debe DICIEMBRE</t>
+  </si>
+  <si>
+    <t>Kromacolor - Materiales para terraza</t>
+  </si>
+  <si>
+    <t>Debito 16/12</t>
+  </si>
+  <si>
+    <t>Transf 05/12</t>
+  </si>
+  <si>
+    <t>Balcazza Leonardo - Resto terraza</t>
+  </si>
+  <si>
+    <t>Dpto. 10 - Materiales - Arreglo perdida caño cloacal - Pago el dpto 10</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1082,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="212">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1341,15 +1320,8 @@
     <xf numFmtId="8" fontId="26" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1357,10 +1329,18 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="25" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1385,6 +1365,12 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1436,8 +1422,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1803,7 +1787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M128"/>
+  <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
@@ -1821,7 +1805,7 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15"/>
       <c r="B1" s="71" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C1" s="71"/>
       <c r="D1" s="71"/>
@@ -1838,19 +1822,19 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
-      <c r="B3" s="187" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="187"/>
-      <c r="D3" s="187"/>
-      <c r="E3" s="188"/>
+      <c r="B3" s="190" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="191"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
@@ -1858,10 +1842,10 @@
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
@@ -1871,7 +1855,7 @@
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
@@ -1881,49 +1865,49 @@
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="192" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="192"/>
+      <c r="B8" s="195" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="195"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="192"/>
-      <c r="C9" s="192"/>
+      <c r="B9" s="195"/>
+      <c r="C9" s="195"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="192"/>
-      <c r="C10" s="192"/>
+      <c r="B10" s="195"/>
+      <c r="C10" s="195"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="191" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="191"/>
-      <c r="C13" s="191"/>
-      <c r="D13" s="191"/>
-      <c r="E13" s="191"/>
+      <c r="A13" s="194" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="194"/>
+      <c r="C13" s="194"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="191"/>
-      <c r="B14" s="191"/>
-      <c r="C14" s="191"/>
-      <c r="D14" s="191"/>
-      <c r="E14" s="191"/>
+      <c r="A14" s="194"/>
+      <c r="B14" s="194"/>
+      <c r="C14" s="194"/>
+      <c r="D14" s="194"/>
+      <c r="E14" s="194"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="191"/>
-      <c r="B15" s="191"/>
-      <c r="C15" s="191"/>
-      <c r="D15" s="191"/>
-      <c r="E15" s="191"/>
+      <c r="A15" s="194"/>
+      <c r="B15" s="194"/>
+      <c r="C15" s="194"/>
+      <c r="D15" s="194"/>
+      <c r="E15" s="194"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="191"/>
-      <c r="B16" s="191"/>
-      <c r="C16" s="191"/>
-      <c r="D16" s="191"/>
-      <c r="E16" s="191"/>
+      <c r="A16" s="194"/>
+      <c r="B16" s="194"/>
+      <c r="C16" s="194"/>
+      <c r="D16" s="194"/>
+      <c r="E16" s="194"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
@@ -1950,7 +1934,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1981,7 +1965,7 @@
     </row>
     <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2009,928 +1993,882 @@
       <c r="D28" s="169"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="169"/>
+      <c r="D29" s="186">
+        <v>490846</v>
+      </c>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="169"/>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="169">
-        <v>0</v>
-      </c>
-      <c r="E31" s="5"/>
-    </row>
-    <row r="32" spans="1:7" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="169"/>
-      <c r="E32" s="5"/>
-    </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="59" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="59"/>
-      <c r="C33" s="59"/>
-      <c r="D33" s="170">
-        <f>SUM(D25:D32)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="143"/>
-    </row>
-    <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="30" t="s">
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="170">
+        <f>SUM(D25:D29)</f>
+        <v>490846</v>
+      </c>
+      <c r="E30" s="143"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="171"/>
-      <c r="E34" s="144">
-        <f>D24+D33</f>
-        <v>772332</v>
-      </c>
-      <c r="F34" s="22"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="36" t="s">
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="171"/>
+      <c r="E31" s="144">
+        <f>D24+D30</f>
+        <v>1263178</v>
+      </c>
+      <c r="F31" s="22"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="172"/>
-      <c r="E35" s="145"/>
-    </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="185" t="s">
-        <v>116</v>
-      </c>
-      <c r="B36" s="186"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="159">
+      <c r="B32" s="36"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="172"/>
+      <c r="E32" s="145"/>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="188" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="189"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="182">
         <v>35000</v>
       </c>
-      <c r="E36" s="146"/>
-    </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="185" t="s">
-        <v>117</v>
-      </c>
-      <c r="B37" s="186"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="173"/>
-      <c r="E37" s="146"/>
-      <c r="H37" s="157" t="s">
+      <c r="E33" s="146"/>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="188" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="189"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="185">
+        <v>112400</v>
+      </c>
+      <c r="E34" s="146"/>
+      <c r="H34" s="157" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="173"/>
+      <c r="E35" s="147">
+        <f>SUM(D33:D34)</f>
+        <v>147400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="174"/>
+      <c r="E36" s="148"/>
+    </row>
+    <row r="37" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="192" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="193"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="184">
+        <f>26570+6696</f>
+        <v>33266</v>
+      </c>
+      <c r="E37" s="160" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="196" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="174"/>
-      <c r="E38" s="147">
-        <f>SUM(D36:D37)</f>
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="36" t="s">
-        <v>32</v>
+      <c r="B38" s="197"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="183">
+        <v>54278</v>
+      </c>
+      <c r="E38" s="149" t="str">
+        <f>E37</f>
+        <v>Debito 02/12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="30" t="s">
+        <v>2</v>
       </c>
       <c r="B39" s="30"/>
       <c r="C39" s="30"/>
-      <c r="D39" s="175"/>
-      <c r="E39" s="148"/>
-    </row>
-    <row r="40" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="189" t="s">
-        <v>96</v>
-      </c>
-      <c r="B40" s="190"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="176">
-        <v>26570</v>
-      </c>
-      <c r="E40" s="160" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="165" t="s">
+      <c r="D39" s="173"/>
+      <c r="E39" s="150">
+        <f>SUM(D37:D38)</f>
+        <v>87544</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="151"/>
+      <c r="C40" s="151"/>
+      <c r="D40" s="175"/>
+      <c r="E40" s="152"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="181">
+        <v>561889.18999999994</v>
+      </c>
+      <c r="E41" s="160" t="s">
+        <v>107</v>
+      </c>
+      <c r="G41" s="127"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="181">
+        <v>10602.27</v>
+      </c>
+      <c r="E42" s="160" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="181">
+        <v>75532.289999999994</v>
+      </c>
+      <c r="E43" s="160" t="str">
+        <f>E42</f>
+        <v>Debito 16/12</v>
+      </c>
+      <c r="G43" s="142"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B41" s="158"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="176">
-        <v>6152</v>
-      </c>
-      <c r="E41" s="160" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="189" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" s="190"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="177">
-        <v>54278</v>
-      </c>
-      <c r="E42" s="149" t="str">
-        <f>E40</f>
-        <v>Debito 04/11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="174"/>
-      <c r="E43" s="150">
-        <f>SUM(D40:D42)</f>
-        <v>87000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" s="151"/>
-      <c r="C44" s="151"/>
-      <c r="D44" s="178"/>
-      <c r="E44" s="152"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="180">
+        <v>79844.990000000005</v>
+      </c>
+      <c r="E44" s="160" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>50</v>
+      <c r="A45" s="5" t="str">
+        <f>A44</f>
+        <v>Sindicatos mes de DICIEMBRE</v>
       </c>
       <c r="B45" s="5"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="211">
-        <v>561889.18999999994</v>
-      </c>
-      <c r="E45" s="160" t="s">
-        <v>107</v>
-      </c>
-      <c r="G45" s="127"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="180">
+        <v>5131.7700000000004</v>
+      </c>
+      <c r="E45" s="161" t="str">
+        <f>E44</f>
+        <v>Debito 12/12</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
-        <v>82</v>
+      <c r="A46" s="5" t="str">
+        <f>A45</f>
+        <v>Sindicatos mes de DICIEMBRE</v>
       </c>
       <c r="B46" s="5"/>
-      <c r="C46" s="54"/>
-      <c r="D46" s="183">
-        <v>10602.27</v>
-      </c>
-      <c r="E46" s="160" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="183">
-        <v>75532.289999999994</v>
-      </c>
-      <c r="E47" s="160" t="str">
-        <f>E46</f>
-        <v>Debito 17/11</v>
-      </c>
-      <c r="G47" s="142"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="180">
+        <v>46185.919999999998</v>
+      </c>
+      <c r="E46" s="162" t="str">
+        <f>E45</f>
+        <v>Debito 12/12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="151"/>
+      <c r="C47" s="151"/>
+      <c r="D47" s="176"/>
+      <c r="E47" s="150">
+        <f>SUM(D41:D46)</f>
+        <v>779186.43</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="210">
-        <v>79844.990000000005</v>
-      </c>
-      <c r="E48" s="160" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="str">
-        <f>A48</f>
-        <v>Sindicatos mes de DICIEMBRE</v>
+      <c r="A48" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="151"/>
+      <c r="C48" s="151"/>
+      <c r="D48" s="175"/>
+      <c r="E48" s="152"/>
+    </row>
+    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="210">
-        <v>5131.7700000000004</v>
-      </c>
-      <c r="E49" s="161" t="str">
-        <f>E48</f>
-        <v>Debito 12/11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="str">
-        <f>A49</f>
-        <v>Sindicatos mes de DICIEMBRE</v>
-      </c>
-      <c r="B50" s="5"/>
+      <c r="D49" s="180">
+        <v>67167.600000000006</v>
+      </c>
+      <c r="E49" s="160" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="163"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="210">
-        <v>46185.919999999998</v>
-      </c>
-      <c r="E50" s="162" t="str">
-        <f>E49</f>
-        <v>Debito 12/11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B51" s="151"/>
-      <c r="C51" s="151"/>
-      <c r="D51" s="179"/>
-      <c r="E51" s="150">
-        <f>SUM(D45:D50)</f>
-        <v>779186.43</v>
+      <c r="D50" s="180">
+        <v>28837.72</v>
+      </c>
+      <c r="E50" s="160" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="180">
+        <v>26548.26</v>
+      </c>
+      <c r="E51" s="160" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B52" s="151"/>
-      <c r="C52" s="151"/>
-      <c r="D52" s="178"/>
-      <c r="E52" s="152"/>
-    </row>
-    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="210">
-        <v>67167.600000000006</v>
-      </c>
-      <c r="E53" s="160" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B54" s="163"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="210">
-        <v>28837.72</v>
-      </c>
-      <c r="E54" s="160" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B55" s="5"/>
+      <c r="A52" s="192" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" s="193"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="180">
+        <v>438036.18</v>
+      </c>
+      <c r="E52" s="160" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="177"/>
+      <c r="E53" s="150">
+        <f>SUM(D49:D52)</f>
+        <v>560589.76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="36"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="173"/>
+      <c r="E54" s="153"/>
+    </row>
+    <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="165" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" s="158"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="210">
-        <v>26548.26</v>
-      </c>
-      <c r="E55" s="160" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="189" t="s">
-        <v>79</v>
-      </c>
-      <c r="B56" s="190"/>
+      <c r="D55" s="180">
+        <v>85000</v>
+      </c>
+      <c r="E55" s="164" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="165" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="158"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="163">
-        <v>426357.06</v>
-      </c>
-      <c r="E56" s="164"/>
-    </row>
-    <row r="57" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="180"/>
-      <c r="E57" s="150">
-        <f>SUM(D53:D56)</f>
-        <v>548910.64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="36"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="174"/>
-      <c r="E58" s="153"/>
+      <c r="D56" s="180">
+        <v>78000</v>
+      </c>
+      <c r="E56" s="164" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="165" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" s="158"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="131">
+        <v>600000</v>
+      </c>
+      <c r="E57" s="164" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="192" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" s="193"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="131">
+        <v>220000</v>
+      </c>
+      <c r="E58" s="164"/>
     </row>
     <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="165" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B59" s="158"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="210">
-        <v>85000</v>
+      <c r="D59" s="131">
+        <v>19726.189999999999</v>
       </c>
       <c r="E59" s="164" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="165" t="s">
-        <v>100</v>
-      </c>
-      <c r="B60" s="158"/>
+      <c r="A60" s="192"/>
+      <c r="B60" s="193"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="210">
-        <v>78000</v>
-      </c>
-      <c r="E60" s="164" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="165" t="s">
-        <v>111</v>
-      </c>
-      <c r="B61" s="158"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="109">
-        <v>500000</v>
-      </c>
-      <c r="E61" s="164" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="165" t="s">
-        <v>112</v>
-      </c>
-      <c r="B62" s="158"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="131">
-        <v>19726.189999999999</v>
-      </c>
-      <c r="E62" s="164" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="189" t="s">
-        <v>102</v>
-      </c>
-      <c r="B63" s="190"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="164"/>
+      <c r="I60" s="192"/>
+      <c r="J60" s="193"/>
+    </row>
+    <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="36"/>
+      <c r="C61" s="36"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="154">
+        <f>SUM(D55:D60)</f>
+        <v>1002726.19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="69"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="171"/>
+      <c r="E62" s="153"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="109">
-        <v>250000</v>
-      </c>
-      <c r="E63" s="184" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="189" t="s">
-        <v>99</v>
-      </c>
-      <c r="B64" s="190"/>
+      <c r="D63" s="180">
+        <v>53000</v>
+      </c>
+      <c r="E63" s="155"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B64" s="5"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="109">
-        <v>45000</v>
-      </c>
-      <c r="E64" s="164" t="s">
-        <v>104</v>
-      </c>
-      <c r="I64" s="189"/>
-      <c r="J64" s="190"/>
+      <c r="D64" s="180">
+        <v>56953.55</v>
+      </c>
+      <c r="E64" s="41"/>
     </row>
     <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="30" t="s">
+      <c r="A65" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" s="53"/>
+      <c r="C65" s="53"/>
+      <c r="D65" s="112"/>
+      <c r="E65" s="106">
+        <f>SUM(D63:D64)</f>
+        <v>109953.55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="105"/>
+      <c r="E66" s="113"/>
+    </row>
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="114"/>
+      <c r="E67" s="115"/>
+    </row>
+    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="1"/>
+      <c r="D68" s="116"/>
+      <c r="E68" s="117"/>
+      <c r="F68" s="45"/>
+    </row>
+    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" s="10"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="118"/>
+      <c r="E69" s="119">
+        <f>(SUM(E27:E67))</f>
+        <v>3950577.93</v>
+      </c>
+      <c r="F69" s="142"/>
+      <c r="G69" s="45"/>
+      <c r="H69" s="127"/>
+      <c r="I69" s="127"/>
+      <c r="J69" s="127"/>
+      <c r="K69" s="127"/>
+      <c r="L69" s="127"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D70" s="116"/>
+      <c r="E70" s="116"/>
+      <c r="H70" s="127"/>
+      <c r="I70" s="127"/>
+      <c r="J70" s="127"/>
+      <c r="K70" s="127"/>
+      <c r="L70" s="127"/>
+    </row>
+    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D71" s="116"/>
+      <c r="E71" s="116"/>
+      <c r="H71" s="178"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="120"/>
+      <c r="E72" s="121"/>
+    </row>
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="192"/>
+      <c r="B73" s="193"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="131"/>
+      <c r="E73" s="107"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="192"/>
+      <c r="B74" s="193"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="109"/>
+      <c r="E74" s="107"/>
+    </row>
+    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="188"/>
+      <c r="B75" s="189"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="109"/>
+      <c r="E75" s="107"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="108"/>
+      <c r="B76" s="110"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="109"/>
+      <c r="E76" s="107"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="51"/>
+      <c r="B77" s="50"/>
+      <c r="C77" s="50"/>
+      <c r="D77" s="60"/>
+      <c r="E77" s="60">
+        <f>SUM(D73:D76)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B80" s="31"/>
+      <c r="C80" s="31"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="104"/>
+    </row>
+    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82" s="10"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="70">
+        <f>E77+E80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="102" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" s="103">
+        <f>E69</f>
+        <v>3950577.93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" s="103">
+        <f>E69-E67</f>
+        <v>3950577.93</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="102" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="103">
+        <f>E82-E80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="102" t="s">
+        <v>41</v>
+      </c>
+      <c r="B87" s="103">
+        <f>E82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="198"/>
+      <c r="B90" s="198"/>
+      <c r="C90" s="198"/>
+      <c r="D90" s="198"/>
+      <c r="E90" s="198"/>
+    </row>
+    <row r="91" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="198"/>
+      <c r="B91" s="198"/>
+      <c r="C91" s="198"/>
+      <c r="D91" s="198"/>
+      <c r="E91" s="198"/>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="198"/>
+      <c r="B92" s="198"/>
+      <c r="C92" s="198"/>
+      <c r="D92" s="198"/>
+      <c r="E92" s="198"/>
+    </row>
+    <row r="94" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B94" s="128"/>
+      <c r="C94" s="24"/>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="34"/>
+      <c r="B95" s="61">
+        <v>0</v>
+      </c>
+      <c r="C95" s="26"/>
+    </row>
+    <row r="96" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" s="41">
+        <f>PRORRATEO!F29</f>
+        <v>3500185.2800000003</v>
+      </c>
+      <c r="C96" s="24"/>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="25"/>
+      <c r="B97" s="41">
+        <v>0</v>
+      </c>
+      <c r="C97" s="24"/>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B98" s="111">
+        <f>B119</f>
+        <v>0</v>
+      </c>
+      <c r="C98" s="24"/>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="28"/>
+      <c r="B99" s="49"/>
+      <c r="C99" s="24"/>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="126" t="s">
+        <v>47</v>
+      </c>
+      <c r="B100" s="49"/>
+      <c r="C100" s="24"/>
+    </row>
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" s="49">
+        <f>-B85</f>
+        <v>-3950577.93</v>
+      </c>
+      <c r="C101" s="24"/>
+    </row>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B102" s="49">
+        <f>-(B86)</f>
+        <v>0</v>
+      </c>
+      <c r="C102" s="24"/>
+    </row>
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B65" s="36"/>
-      <c r="C65" s="36"/>
-      <c r="D65" s="35"/>
-      <c r="E65" s="154">
-        <f>SUM(D59:D64)</f>
-        <v>977726.19</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="B66" s="69"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="171"/>
-      <c r="E66" s="153"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="163">
-        <v>53000</v>
-      </c>
-      <c r="E67" s="155"/>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="163">
-        <v>56054.17</v>
-      </c>
-      <c r="E68" s="41"/>
-    </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="B69" s="53"/>
-      <c r="C69" s="53"/>
-      <c r="D69" s="112"/>
-      <c r="E69" s="106">
-        <f>SUM(D67:D68)</f>
-        <v>109054.17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="105"/>
-      <c r="E70" s="113"/>
-    </row>
-    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="31" t="s">
+      <c r="B103" s="61">
+        <f>SUM(B95:B102)</f>
+        <v>-450392.64999999991</v>
+      </c>
+      <c r="C103" s="27"/>
+      <c r="D103" s="45"/>
+    </row>
+    <row r="104" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="42"/>
+      <c r="C104" s="27"/>
+      <c r="D104" s="45"/>
+      <c r="E104" s="129"/>
+      <c r="F104" s="130"/>
+    </row>
+    <row r="105" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B105" s="43"/>
+      <c r="C105" s="27"/>
+    </row>
+    <row r="106" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106"/>
+      <c r="B106" s="42"/>
+      <c r="C106" s="38"/>
+    </row>
+    <row r="107" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="134" t="s">
+        <v>88</v>
+      </c>
+      <c r="B107" s="135">
+        <v>220559.39390000375</v>
+      </c>
+      <c r="C107" s="38"/>
+      <c r="D107" s="48"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B108" s="140">
+        <f>-B85</f>
+        <v>-3950577.93</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B71" s="31"/>
-      <c r="C71" s="31"/>
-      <c r="D71" s="114"/>
-      <c r="E71" s="115">
-        <f>3774269.17-3585092.73</f>
-        <v>189176.43999999994</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="1"/>
-      <c r="D72" s="116"/>
-      <c r="E72" s="117"/>
-      <c r="F72" s="45"/>
-    </row>
-    <row r="73" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B73" s="10"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="118"/>
-      <c r="E73" s="119">
-        <f>(SUM(E27:E71))+400786</f>
-        <v>3899171.87</v>
-      </c>
-      <c r="F73" s="142"/>
-      <c r="G73" s="45"/>
-      <c r="H73" s="157" t="s">
-        <v>113</v>
-      </c>
-      <c r="I73" s="157"/>
-      <c r="J73" s="157"/>
-      <c r="K73" s="157"/>
-      <c r="L73" s="157"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D74" s="116"/>
-      <c r="E74" s="116"/>
-      <c r="H74" s="157"/>
-      <c r="I74" s="157"/>
-      <c r="J74" s="157"/>
-      <c r="K74" s="157"/>
-      <c r="L74" s="157"/>
-    </row>
-    <row r="75" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D75" s="116"/>
-      <c r="E75" s="116"/>
-      <c r="H75" s="181"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="120"/>
-      <c r="E76" s="121"/>
-    </row>
-    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="189"/>
-      <c r="B77" s="190"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="131"/>
-      <c r="E77" s="107"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="189"/>
-      <c r="B78" s="190"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="109"/>
-      <c r="E78" s="107"/>
-    </row>
-    <row r="79" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="185"/>
-      <c r="B79" s="186"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="109"/>
-      <c r="E79" s="107"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="108"/>
-      <c r="B80" s="110"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="109"/>
-      <c r="E80" s="107"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="51"/>
-      <c r="B81" s="50"/>
-      <c r="C81" s="50"/>
-      <c r="D81" s="60"/>
-      <c r="E81" s="60">
-        <f>SUM(D77:D80)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B84" s="31"/>
-      <c r="C84" s="31"/>
-      <c r="D84" s="32"/>
-      <c r="E84" s="104"/>
-    </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B86" s="10"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="70">
-        <f>E81+E84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="102" t="s">
-        <v>14</v>
-      </c>
-      <c r="B88" s="103">
-        <f>E73</f>
-        <v>3899171.87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" s="103">
-        <f>E73-E71</f>
-        <v>3709995.43</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="102" t="s">
-        <v>22</v>
-      </c>
-      <c r="B90" s="103">
-        <f>E86-E84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="102" t="s">
-        <v>43</v>
-      </c>
-      <c r="B91" s="103">
-        <f>E86</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="193"/>
-      <c r="B94" s="193"/>
-      <c r="C94" s="193"/>
-      <c r="D94" s="193"/>
-      <c r="E94" s="193"/>
-    </row>
-    <row r="95" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="193"/>
-      <c r="B95" s="193"/>
-      <c r="C95" s="193"/>
-      <c r="D95" s="193"/>
-      <c r="E95" s="193"/>
-    </row>
-    <row r="96" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="193"/>
-      <c r="B96" s="193"/>
-      <c r="C96" s="193"/>
-      <c r="D96" s="193"/>
-      <c r="E96" s="193"/>
-    </row>
-    <row r="98" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B98" s="128"/>
-      <c r="C98" s="24"/>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="34"/>
-      <c r="B99" s="61">
-        <v>0</v>
-      </c>
-      <c r="C99" s="26"/>
-    </row>
-    <row r="100" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B100" s="41">
+      <c r="B109" s="140">
+        <f>-B86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B110" s="140">
+        <f>B119</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="B111" s="141">
         <f>PRORRATEO!F29</f>
-        <v>3472658.2500000005</v>
-      </c>
-      <c r="C100" s="24"/>
-    </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="25"/>
-      <c r="B101" s="41">
-        <v>0</v>
-      </c>
-      <c r="C101" s="24"/>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B102" s="111">
-        <f>B123</f>
-        <v>0</v>
-      </c>
-      <c r="C102" s="24"/>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="28"/>
-      <c r="B103" s="49"/>
-      <c r="C103" s="24"/>
-    </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="126" t="s">
+        <v>3500185.2800000003</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="B104" s="49"/>
-      <c r="C104" s="24"/>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B105" s="49">
-        <f>-B89</f>
-        <v>-3709995.43</v>
-      </c>
-      <c r="C105" s="24"/>
-    </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B106" s="49">
-        <f>-(B90)</f>
-        <v>0</v>
-      </c>
-      <c r="C106" s="24"/>
-    </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="33" t="s">
+      <c r="B112" s="139">
+        <f>SUM(B107:C111)</f>
+        <v>-229833.25609999616</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A113" s="136"/>
+      <c r="B113" s="136"/>
+    </row>
+    <row r="114" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A115" s="199" t="s">
+        <v>33</v>
+      </c>
+      <c r="B115" s="199"/>
+      <c r="C115" s="199"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A116" s="199"/>
+      <c r="B116" s="199"/>
+      <c r="C116" s="199"/>
+    </row>
+    <row r="117" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="123"/>
+      <c r="B117" s="37"/>
+      <c r="C117" s="37">
+        <v>40000</v>
+      </c>
+      <c r="E117" s="142"/>
+    </row>
+    <row r="118" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="123"/>
+      <c r="B118" s="125"/>
+      <c r="C118" s="122"/>
+      <c r="D118" s="142"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B107" s="61">
-        <f>SUM(B99:B106)</f>
-        <v>-237337.1799999997</v>
-      </c>
-      <c r="C107" s="27"/>
-      <c r="D107" s="45"/>
-    </row>
-    <row r="108" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="42"/>
-      <c r="C108" s="27"/>
-      <c r="D108" s="45"/>
-      <c r="E108" s="129"/>
-      <c r="F108" s="130"/>
-    </row>
-    <row r="109" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B109" s="43"/>
-      <c r="C109" s="27"/>
-    </row>
-    <row r="110" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110"/>
-      <c r="B110" s="42"/>
-      <c r="C110" s="38"/>
-    </row>
-    <row r="111" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="134" t="s">
-        <v>90</v>
-      </c>
-      <c r="B111" s="135">
-        <v>220559.39390000375</v>
-      </c>
-      <c r="C111" s="38"/>
-      <c r="D111" s="48"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="56" t="s">
-        <v>54</v>
-      </c>
-      <c r="B112" s="140">
-        <f>-B89</f>
-        <v>-3709995.43</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="B113" s="140">
-        <f>-B90</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="B114" s="140">
-        <f>B123</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="B115" s="141">
-        <f>PRORRATEO!F29</f>
-        <v>3472658.2500000005</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="138" t="s">
-        <v>51</v>
-      </c>
-      <c r="B116" s="139">
-        <f>SUM(B111:C115)</f>
-        <v>-16777.786099995952</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="136"/>
-      <c r="B117" s="136"/>
-    </row>
-    <row r="118" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="194" t="s">
-        <v>33</v>
-      </c>
-      <c r="B119" s="194"/>
-      <c r="C119" s="194"/>
+      <c r="B119" s="124">
+        <f>SUM(B117:B118)</f>
+        <v>0</v>
+      </c>
+      <c r="C119" s="47"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="194"/>
-      <c r="B120" s="194"/>
-      <c r="C120" s="194"/>
-    </row>
-    <row r="121" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="123"/>
-      <c r="B121" s="37"/>
-      <c r="C121" s="37">
-        <v>40000</v>
-      </c>
-      <c r="E121" s="142"/>
-    </row>
-    <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="123"/>
-      <c r="B122" s="125"/>
-      <c r="C122" s="122"/>
-      <c r="D122" s="142"/>
+      <c r="M120" s="8"/>
+    </row>
+    <row r="121" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="198"/>
+      <c r="B121" s="198"/>
+      <c r="C121" s="198"/>
+      <c r="D121" s="198"/>
+      <c r="E121" s="198"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A122" s="198"/>
+      <c r="B122" s="198"/>
+      <c r="C122" s="198"/>
+      <c r="D122" s="198"/>
+      <c r="E122" s="198"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="B123" s="124">
-        <f>SUM(B121:B122)</f>
-        <v>0</v>
-      </c>
-      <c r="C123" s="47"/>
+      <c r="A123" s="198"/>
+      <c r="B123" s="198"/>
+      <c r="C123" s="198"/>
+      <c r="D123" s="198"/>
+      <c r="E123" s="198"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M124" s="8"/>
-    </row>
-    <row r="125" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="193"/>
-      <c r="B125" s="193"/>
-      <c r="C125" s="193"/>
-      <c r="D125" s="193"/>
-      <c r="E125" s="193"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A126" s="193"/>
-      <c r="B126" s="193"/>
-      <c r="C126" s="193"/>
-      <c r="D126" s="193"/>
-      <c r="E126" s="193"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A127" s="193"/>
-      <c r="B127" s="193"/>
-      <c r="C127" s="193"/>
-      <c r="D127" s="193"/>
-      <c r="E127" s="193"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A128" s="193"/>
-      <c r="B128" s="193"/>
-      <c r="C128" s="193"/>
-      <c r="D128" s="193"/>
-      <c r="E128" s="193"/>
+      <c r="A124" s="198"/>
+      <c r="B124" s="198"/>
+      <c r="C124" s="198"/>
+      <c r="D124" s="198"/>
+      <c r="E124" s="198"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A125:E128"/>
-    <mergeCell ref="A119:C120"/>
-    <mergeCell ref="A94:E96"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A121:E124"/>
+    <mergeCell ref="A115:C116"/>
+    <mergeCell ref="A90:E92"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A58:B58"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2966,15 +2904,15 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="200"/>
+      <c r="H1" s="200"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="200"/>
+      <c r="K1" s="200"/>
+      <c r="L1" s="200"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
@@ -2983,7 +2921,7 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="166">
@@ -2993,7 +2931,7 @@
       <c r="H2" s="6"/>
       <c r="I2" s="7"/>
       <c r="J2" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="133">
@@ -3020,75 +2958,75 @@
       <c r="N3" s="62"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="200" t="s">
+      <c r="A4" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="200" t="s">
+      <c r="B4" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="200" t="s">
+      <c r="C4" s="205" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="200" t="s">
+      <c r="D4" s="205" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="196" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="200" t="s">
+      <c r="E4" s="201" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="202" t="s">
+      <c r="G4" s="207" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="196" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="196" t="s">
+      <c r="H4" s="201" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="201" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="196" t="s">
+      <c r="J4" s="201" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="205" t="s">
-        <v>85</v>
+      <c r="K4" s="210" t="s">
+        <v>83</v>
       </c>
       <c r="L4" s="65" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="198" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" s="203" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="207" t="s">
-        <v>38</v>
+      <c r="N4" s="212" t="s">
+        <v>37</v>
       </c>
       <c r="Q4" s="45"/>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="201"/>
-      <c r="B5" s="201"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="197"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="197"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="197"/>
-      <c r="K5" s="206"/>
+      <c r="A5" s="206"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="214"/>
+      <c r="D5" s="206"/>
+      <c r="E5" s="202"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="202"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="202"/>
+      <c r="K5" s="211"/>
       <c r="L5" s="63" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/01</v>
       </c>
-      <c r="M5" s="199"/>
-      <c r="N5" s="208"/>
+      <c r="M5" s="204"/>
+      <c r="N5" s="213"/>
     </row>
     <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="66">
         <v>1</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" s="66"/>
       <c r="D6" s="75">
@@ -3097,7 +3035,7 @@
       <c r="E6" s="76">
         <v>258261.01</v>
       </c>
-      <c r="F6" s="78">
+      <c r="F6" s="187">
         <f>E6</f>
         <v>258261.01</v>
       </c>
@@ -3142,25 +3080,23 @@
         <v>2</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="67"/>
       <c r="D7" s="75">
         <v>5.88</v>
       </c>
       <c r="E7" s="76">
-        <v>704907.02</v>
-      </c>
-      <c r="F7" s="78">
-        <v>200000</v>
-      </c>
+        <v>747046.02</v>
+      </c>
+      <c r="F7" s="78"/>
       <c r="G7" s="79">
         <f t="shared" si="0"/>
-        <v>504907.02</v>
+        <v>747046.02</v>
       </c>
       <c r="H7" s="79">
         <f t="shared" ref="H7:H23" si="2">IF(G7&gt;0,G7*3%,0)</f>
-        <v>15147.2106</v>
+        <v>22411.3806</v>
       </c>
       <c r="I7" s="80">
         <v>0</v>
@@ -3175,15 +3111,15 @@
       </c>
       <c r="L7" s="83">
         <f t="shared" ref="L7:L23" si="4">ROUND(SUM(G7:K7),0) + O7</f>
-        <v>747046.02</v>
+        <v>996449.02</v>
       </c>
       <c r="M7" s="84">
         <f t="shared" ref="M7:M23" si="5">ROUND(L7*6% + L7,0) + O7</f>
-        <v>791869.02</v>
+        <v>1056236.02</v>
       </c>
       <c r="N7" s="85">
         <f t="shared" ref="N7:N23" si="6">ROUND(L7*3%,0) + L7</f>
-        <v>769457.02</v>
+        <v>1026342.02</v>
       </c>
       <c r="O7" s="45">
         <f>O6+0.01</f>
@@ -3197,26 +3133,23 @@
         <v>3</v>
       </c>
       <c r="B8" s="66" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" s="67"/>
       <c r="D8" s="75">
         <v>6.65</v>
       </c>
       <c r="E8" s="76">
-        <v>264650.03000000003</v>
-      </c>
-      <c r="F8" s="78">
-        <f>E8</f>
-        <v>264650.03000000003</v>
-      </c>
+        <v>256717.03</v>
+      </c>
+      <c r="F8" s="78"/>
       <c r="G8" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>256717.03</v>
       </c>
       <c r="H8" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7701.5108999999993</v>
       </c>
       <c r="I8" s="80">
         <v>0</v>
@@ -3231,15 +3164,15 @@
       </c>
       <c r="L8" s="83">
         <f t="shared" si="4"/>
-        <v>256717.03</v>
+        <v>521135.03</v>
       </c>
       <c r="M8" s="84">
         <f t="shared" si="5"/>
-        <v>272120.03000000003</v>
+        <v>552403.03</v>
       </c>
       <c r="N8" s="85">
         <f t="shared" si="6"/>
-        <v>264419.03000000003</v>
+        <v>536769.03</v>
       </c>
       <c r="O8" s="45">
         <f t="shared" ref="O8:O24" si="8">O7+0.01</f>
@@ -3252,18 +3185,18 @@
         <v>4</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="75">
         <v>6.73</v>
       </c>
       <c r="E9" s="76">
-        <v>259805.04</v>
-      </c>
-      <c r="F9" s="78">
+        <v>267599.03999999998</v>
+      </c>
+      <c r="F9" s="187">
         <f t="shared" ref="F9:F23" si="9">E9</f>
-        <v>259805.04</v>
+        <v>267599.03999999998</v>
       </c>
       <c r="G9" s="79">
         <f t="shared" si="0"/>
@@ -3308,23 +3241,26 @@
         <v>5</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10" s="67"/>
       <c r="D10" s="75">
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="76">
-        <v>309402.05</v>
-      </c>
-      <c r="F10" s="78"/>
+        <v>647933.05000000005</v>
+      </c>
+      <c r="F10" s="187">
+        <f>E10</f>
+        <v>647933.05000000005</v>
+      </c>
       <c r="G10" s="79">
         <f t="shared" si="0"/>
-        <v>309402.05</v>
+        <v>0</v>
       </c>
       <c r="H10" s="79">
         <f t="shared" si="2"/>
-        <v>9282.0614999999998</v>
+        <v>0</v>
       </c>
       <c r="I10" s="80">
         <v>0</v>
@@ -3339,15 +3275,15 @@
       </c>
       <c r="L10" s="83">
         <f t="shared" si="4"/>
-        <v>629061.05000000005</v>
+        <v>310376.05</v>
       </c>
       <c r="M10" s="84">
         <f t="shared" si="5"/>
-        <v>666805.05000000005</v>
+        <v>328999.05</v>
       </c>
       <c r="N10" s="85">
         <f t="shared" si="6"/>
-        <v>647933.05000000005</v>
+        <v>319687.05</v>
       </c>
       <c r="O10" s="45">
         <f t="shared" si="8"/>
@@ -3361,7 +3297,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C11" s="66"/>
       <c r="D11" s="75">
@@ -3370,7 +3306,7 @@
       <c r="E11" s="76">
         <v>182597.06</v>
       </c>
-      <c r="F11" s="78">
+      <c r="F11" s="187">
         <f t="shared" si="9"/>
         <v>182597.06</v>
       </c>
@@ -3416,7 +3352,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C12" s="66"/>
       <c r="D12" s="75">
@@ -3425,17 +3361,14 @@
       <c r="E12" s="76">
         <v>218885.07</v>
       </c>
-      <c r="F12" s="78">
-        <f>E12</f>
-        <v>218885.07</v>
-      </c>
+      <c r="F12" s="78"/>
       <c r="G12" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>218885.07</v>
       </c>
       <c r="H12" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6566.5520999999999</v>
       </c>
       <c r="I12" s="80">
         <v>0</v>
@@ -3450,15 +3383,15 @@
       </c>
       <c r="L12" s="83">
         <f t="shared" si="4"/>
-        <v>218885.07</v>
+        <v>444337.07</v>
       </c>
       <c r="M12" s="84">
         <f t="shared" si="5"/>
-        <v>232018.07</v>
+        <v>470997.07</v>
       </c>
       <c r="N12" s="85">
         <f t="shared" si="6"/>
-        <v>225452.07</v>
+        <v>457667.07</v>
       </c>
       <c r="O12" s="45">
         <f t="shared" si="8"/>
@@ -3471,26 +3404,26 @@
         <v>8</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="67"/>
       <c r="D13" s="75">
         <v>5.67</v>
       </c>
       <c r="E13" s="76">
-        <v>385635.08</v>
-      </c>
-      <c r="F13" s="78">
-        <f>100000+71550+214085</f>
-        <v>385635</v>
+        <v>218885.08</v>
+      </c>
+      <c r="F13" s="187">
+        <f>E13</f>
+        <v>218885.08</v>
       </c>
       <c r="G13" s="79">
         <f t="shared" si="0"/>
-        <v>8.0000000016298145E-2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="79">
         <f t="shared" si="2"/>
-        <v>2.4000000004889442E-3</v>
+        <v>0</v>
       </c>
       <c r="I13" s="80">
         <v>0</v>
@@ -3520,7 +3453,7 @@
         <v>0.08</v>
       </c>
       <c r="Q13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -3529,7 +3462,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="66" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C14" s="67"/>
       <c r="D14" s="75">
@@ -3538,7 +3471,7 @@
       <c r="E14" s="76">
         <v>296093.09000000003</v>
       </c>
-      <c r="F14" s="78">
+      <c r="F14" s="187">
         <f t="shared" si="9"/>
         <v>296093.09000000003</v>
       </c>
@@ -3584,7 +3517,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C15" s="67"/>
       <c r="D15" s="75">
@@ -3593,13 +3526,13 @@
       <c r="E15" s="76">
         <v>189160.1</v>
       </c>
-      <c r="F15" s="78">
-        <f>E15</f>
-        <v>189160.1</v>
+      <c r="F15" s="187">
+        <f>E15+RESUMEN!D58</f>
+        <v>409160.1</v>
       </c>
       <c r="G15" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-219999.99999999997</v>
       </c>
       <c r="H15" s="79">
         <f t="shared" si="2"/>
@@ -3618,15 +3551,15 @@
       </c>
       <c r="L15" s="83">
         <f t="shared" si="4"/>
-        <v>189160.1</v>
+        <v>-30839.9</v>
       </c>
       <c r="M15" s="84">
         <f t="shared" si="5"/>
-        <v>200510.1</v>
+        <v>-32689.9</v>
       </c>
       <c r="N15" s="85">
         <f t="shared" si="6"/>
-        <v>194835.1</v>
+        <v>-31764.9</v>
       </c>
       <c r="O15" s="45">
         <f t="shared" si="8"/>
@@ -3639,7 +3572,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="66" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16" s="67"/>
       <c r="D16" s="75">
@@ -3648,7 +3581,7 @@
       <c r="E16" s="76">
         <v>217341.11</v>
       </c>
-      <c r="F16" s="78">
+      <c r="F16" s="187">
         <f t="shared" si="9"/>
         <v>217341.11</v>
       </c>
@@ -3694,7 +3627,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C17" s="67"/>
       <c r="D17" s="75">
@@ -3703,7 +3636,7 @@
       <c r="E17" s="76">
         <v>214252.12</v>
       </c>
-      <c r="F17" s="78">
+      <c r="F17" s="187">
         <f t="shared" si="9"/>
         <v>214252.12</v>
       </c>
@@ -3749,7 +3682,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="66" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C18" s="67"/>
       <c r="D18" s="75">
@@ -3758,7 +3691,7 @@
       <c r="E18" s="76">
         <v>426961.13</v>
       </c>
-      <c r="F18" s="78">
+      <c r="F18" s="187">
         <f>E18</f>
         <v>426961.13</v>
       </c>
@@ -3804,23 +3737,23 @@
         <v>14</v>
       </c>
       <c r="B19" s="66" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C19" s="67"/>
       <c r="D19" s="75">
         <v>3.3</v>
       </c>
       <c r="E19" s="76">
-        <v>437082.14</v>
+        <v>577588.14</v>
       </c>
       <c r="F19" s="78"/>
       <c r="G19" s="79">
         <f t="shared" si="0"/>
-        <v>437082.14</v>
+        <v>577588.14</v>
       </c>
       <c r="H19" s="79">
         <f t="shared" si="2"/>
-        <v>13112.4642</v>
+        <v>17327.644199999999</v>
       </c>
       <c r="I19" s="80">
         <v>0</v>
@@ -3835,15 +3768,15 @@
       </c>
       <c r="L19" s="83">
         <f t="shared" si="4"/>
-        <v>577588.14</v>
+        <v>722309.14</v>
       </c>
       <c r="M19" s="84">
         <f t="shared" si="5"/>
-        <v>612243.14</v>
+        <v>765648.14</v>
       </c>
       <c r="N19" s="85">
         <f t="shared" si="6"/>
-        <v>594916.14</v>
+        <v>743978.14</v>
       </c>
       <c r="O19" s="45">
         <f t="shared" si="8"/>
@@ -3856,7 +3789,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C20" s="67"/>
       <c r="D20" s="75">
@@ -3865,13 +3798,12 @@
       <c r="E20" s="76">
         <v>69487.149999999994</v>
       </c>
-      <c r="F20" s="78">
-        <f>E20</f>
-        <v>69487.149999999994</v>
+      <c r="F20" s="187">
+        <v>71572.149999999994</v>
       </c>
       <c r="G20" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2085</v>
       </c>
       <c r="H20" s="79">
         <f t="shared" si="2"/>
@@ -3890,15 +3822,15 @@
       </c>
       <c r="L20" s="83">
         <f t="shared" si="4"/>
-        <v>69487.149999999994</v>
+        <v>67402.149999999994</v>
       </c>
       <c r="M20" s="84">
         <f t="shared" si="5"/>
-        <v>73656.149999999994</v>
+        <v>71446.149999999994</v>
       </c>
       <c r="N20" s="85">
         <f t="shared" si="6"/>
-        <v>71572.149999999994</v>
+        <v>69424.149999999994</v>
       </c>
       <c r="O20" s="45">
         <f t="shared" si="8"/>
@@ -3911,7 +3843,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="66" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C21" s="66"/>
       <c r="D21" s="75">
@@ -3920,7 +3852,7 @@
       <c r="E21" s="76">
         <v>124305.16</v>
       </c>
-      <c r="F21" s="78">
+      <c r="F21" s="187">
         <f>E21</f>
         <v>124305.16</v>
       </c>
@@ -3967,25 +3899,25 @@
         <v>17</v>
       </c>
       <c r="B22" s="66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C22" s="67"/>
       <c r="D22" s="75">
         <v>2.61</v>
       </c>
       <c r="E22" s="77">
-        <v>100757.17</v>
+        <v>204536.17</v>
       </c>
       <c r="F22" s="78">
         <v>0</v>
       </c>
       <c r="G22" s="79">
         <f t="shared" si="0"/>
-        <v>100757.17</v>
+        <v>204536.17</v>
       </c>
       <c r="H22" s="79">
         <f t="shared" si="2"/>
-        <v>3022.7150999999999</v>
+        <v>6136.0851000000002</v>
       </c>
       <c r="I22" s="80">
         <v>0</v>
@@ -4000,15 +3932,15 @@
       </c>
       <c r="L22" s="83">
         <f t="shared" si="4"/>
-        <v>204536.17</v>
+        <v>311429.17</v>
       </c>
       <c r="M22" s="84">
         <f t="shared" si="5"/>
-        <v>216808.17</v>
+        <v>330115.17</v>
       </c>
       <c r="N22" s="85">
         <f t="shared" si="6"/>
-        <v>210672.17</v>
+        <v>320772.17</v>
       </c>
       <c r="O22" s="45">
         <f t="shared" si="8"/>
@@ -4021,7 +3953,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="66" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C23" s="132"/>
       <c r="D23" s="75">
@@ -4030,7 +3962,7 @@
       <c r="E23" s="76">
         <v>165225.18</v>
       </c>
-      <c r="F23" s="78">
+      <c r="F23" s="187">
         <f t="shared" si="9"/>
         <v>165225.18</v>
       </c>
@@ -4168,19 +4100,19 @@
       </c>
       <c r="E29" s="55">
         <f>SUM(E6:E28)</f>
-        <v>4824806.71</v>
+        <v>5282872.71</v>
       </c>
       <c r="F29" s="64">
         <f>SUM(F6:F28)</f>
-        <v>3472658.2500000005</v>
+        <v>3500185.2800000003</v>
       </c>
       <c r="G29" s="64">
         <f>SUM(G6:G28)</f>
-        <v>1352148.46</v>
+        <v>1782687.4300000002</v>
       </c>
       <c r="H29" s="64">
         <f t="shared" ref="H29:M29" si="10">SUM(H6:H28)</f>
-        <v>40564.453800000003</v>
+        <v>60143.17289999999</v>
       </c>
       <c r="I29" s="64">
         <f t="shared" si="10"/>
@@ -4196,15 +4128,15 @@
       </c>
       <c r="L29" s="100">
         <f>SUM(L6:L23)</f>
-        <v>5256206.71</v>
+        <v>5706323.71</v>
       </c>
       <c r="M29" s="100">
         <f t="shared" si="10"/>
-        <v>5571580.71</v>
+        <v>6048705.71</v>
       </c>
       <c r="N29" s="100">
         <f>SUM(N6:N28)</f>
-        <v>5413895.71</v>
+        <v>5877513.71</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4213,85 +4145,85 @@
     </row>
     <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="193" t="str">
+      <c r="B32" s="198" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="193"/>
-      <c r="D32" s="193"/>
-      <c r="E32" s="193"/>
-      <c r="F32" s="193"/>
-      <c r="G32" s="193"/>
-      <c r="H32" s="193"/>
-      <c r="I32" s="193"/>
-      <c r="J32" s="193"/>
-      <c r="K32" s="193"/>
-      <c r="L32" s="193"/>
+      <c r="C32" s="198"/>
+      <c r="D32" s="198"/>
+      <c r="E32" s="198"/>
+      <c r="F32" s="198"/>
+      <c r="G32" s="198"/>
+      <c r="H32" s="198"/>
+      <c r="I32" s="198"/>
+      <c r="J32" s="198"/>
+      <c r="K32" s="198"/>
+      <c r="L32" s="198"/>
     </row>
     <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="193"/>
-      <c r="C33" s="193"/>
-      <c r="D33" s="193"/>
-      <c r="E33" s="193"/>
-      <c r="F33" s="193"/>
-      <c r="G33" s="193"/>
-      <c r="H33" s="193"/>
-      <c r="I33" s="193"/>
-      <c r="J33" s="193"/>
-      <c r="K33" s="193"/>
-      <c r="L33" s="193"/>
+      <c r="B33" s="198"/>
+      <c r="C33" s="198"/>
+      <c r="D33" s="198"/>
+      <c r="E33" s="198"/>
+      <c r="F33" s="198"/>
+      <c r="G33" s="198"/>
+      <c r="H33" s="198"/>
+      <c r="I33" s="198"/>
+      <c r="J33" s="198"/>
+      <c r="K33" s="198"/>
+      <c r="L33" s="198"/>
     </row>
     <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="193"/>
-      <c r="C34" s="193"/>
-      <c r="D34" s="193"/>
-      <c r="E34" s="193"/>
-      <c r="F34" s="193"/>
-      <c r="G34" s="193"/>
-      <c r="H34" s="193"/>
-      <c r="I34" s="193"/>
-      <c r="J34" s="193"/>
-      <c r="K34" s="193"/>
-      <c r="L34" s="193"/>
+      <c r="B34" s="198"/>
+      <c r="C34" s="198"/>
+      <c r="D34" s="198"/>
+      <c r="E34" s="198"/>
+      <c r="F34" s="198"/>
+      <c r="G34" s="198"/>
+      <c r="H34" s="198"/>
+      <c r="I34" s="198"/>
+      <c r="J34" s="198"/>
+      <c r="K34" s="198"/>
+      <c r="L34" s="198"/>
     </row>
     <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="193"/>
-      <c r="C35" s="193"/>
-      <c r="D35" s="193"/>
-      <c r="E35" s="193"/>
-      <c r="F35" s="193"/>
-      <c r="G35" s="193"/>
-      <c r="H35" s="193"/>
-      <c r="I35" s="193"/>
-      <c r="J35" s="193"/>
-      <c r="K35" s="193"/>
-      <c r="L35" s="193"/>
+      <c r="B35" s="198"/>
+      <c r="C35" s="198"/>
+      <c r="D35" s="198"/>
+      <c r="E35" s="198"/>
+      <c r="F35" s="198"/>
+      <c r="G35" s="198"/>
+      <c r="H35" s="198"/>
+      <c r="I35" s="198"/>
+      <c r="J35" s="198"/>
+      <c r="K35" s="198"/>
+      <c r="L35" s="198"/>
     </row>
     <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="193"/>
-      <c r="C36" s="193"/>
-      <c r="D36" s="193"/>
-      <c r="E36" s="193"/>
-      <c r="F36" s="193"/>
-      <c r="G36" s="193"/>
-      <c r="H36" s="193"/>
-      <c r="I36" s="193"/>
-      <c r="J36" s="193"/>
-      <c r="K36" s="193"/>
-      <c r="L36" s="193"/>
+      <c r="B36" s="198"/>
+      <c r="C36" s="198"/>
+      <c r="D36" s="198"/>
+      <c r="E36" s="198"/>
+      <c r="F36" s="198"/>
+      <c r="G36" s="198"/>
+      <c r="H36" s="198"/>
+      <c r="I36" s="198"/>
+      <c r="J36" s="198"/>
+      <c r="K36" s="198"/>
+      <c r="L36" s="198"/>
     </row>
     <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="193"/>
-      <c r="C37" s="193"/>
-      <c r="D37" s="193"/>
-      <c r="E37" s="193"/>
-      <c r="F37" s="193"/>
-      <c r="G37" s="193"/>
-      <c r="H37" s="193"/>
-      <c r="I37" s="193"/>
-      <c r="J37" s="193"/>
-      <c r="K37" s="193"/>
-      <c r="L37" s="193"/>
+      <c r="B37" s="198"/>
+      <c r="C37" s="198"/>
+      <c r="D37" s="198"/>
+      <c r="E37" s="198"/>
+      <c r="F37" s="198"/>
+      <c r="G37" s="198"/>
+      <c r="H37" s="198"/>
+      <c r="I37" s="198"/>
+      <c r="J37" s="198"/>
+      <c r="K37" s="198"/>
+      <c r="L37" s="198"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -4322,11 +4254,11 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="5" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C5" s="182" t="s">
-        <v>91</v>
+      <c r="C5" s="179" t="s">
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/YRIGOYEN 7630/Diciembre/YRIGOYEN7630-Diciembre.xlsx
+++ b/YRIGOYEN 7630/Diciembre/YRIGOYEN7630-Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 7630\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 7630\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D03CD6-3AF5-4A24-93E9-35201377AAE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591678AF-78E0-4554-BF33-286E059A6DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="117">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -372,6 +372,12 @@
   </si>
   <si>
     <t>Dpto. 10 - Materiales - Arreglo perdida caño cloacal - Pago el dpto 10</t>
+  </si>
+  <si>
+    <t>Julio Doartero - Trabajo de plomeria en destapacion</t>
+  </si>
+  <si>
+    <t>Transf 30/12</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1088,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1329,18 +1335,6 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="25" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1365,12 +1359,6 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1422,6 +1410,14 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1788,21 +1784,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M124"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15"/>
       <c r="B1" s="71" t="s">
         <v>55</v>
@@ -1811,7 +1807,7 @@
       <c r="D1" s="71"/>
       <c r="E1" s="72"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="73" t="s">
         <v>28</v>
@@ -1820,16 +1816,16 @@
       <c r="D2" s="73"/>
       <c r="E2" s="74"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="190" t="s">
+      <c r="B3" s="182" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="191"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="183"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1840,7 +1836,7 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>57</v>
       </c>
@@ -1853,7 +1849,7 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>56</v>
       </c>
@@ -1864,57 +1860,57 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="195" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="187" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="195"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="195"/>
-      <c r="C9" s="195"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="195"/>
-      <c r="C10" s="195"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="194" t="s">
+      <c r="C8" s="187"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="187"/>
+      <c r="C9" s="187"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="187"/>
+      <c r="C10" s="187"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="186" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="194"/>
-      <c r="C13" s="194"/>
-      <c r="D13" s="194"/>
-      <c r="E13" s="194"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="194"/>
-      <c r="B14" s="194"/>
-      <c r="C14" s="194"/>
-      <c r="D14" s="194"/>
-      <c r="E14" s="194"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="194"/>
-      <c r="B15" s="194"/>
-      <c r="C15" s="194"/>
-      <c r="D15" s="194"/>
-      <c r="E15" s="194"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="194"/>
-      <c r="B16" s="194"/>
-      <c r="C16" s="194"/>
-      <c r="D16" s="194"/>
-      <c r="E16" s="194"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="186"/>
+      <c r="C13" s="186"/>
+      <c r="D13" s="186"/>
+      <c r="E13" s="186"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="186"/>
+      <c r="B14" s="186"/>
+      <c r="C14" s="186"/>
+      <c r="D14" s="186"/>
+      <c r="E14" s="186"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="186"/>
+      <c r="B15" s="186"/>
+      <c r="C15" s="186"/>
+      <c r="D15" s="186"/>
+      <c r="E15" s="186"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="186"/>
+      <c r="B16" s="186"/>
+      <c r="C16" s="186"/>
+      <c r="D16" s="186"/>
+      <c r="E16" s="186"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
@@ -1923,7 +1919,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
         <v>35</v>
       </c>
@@ -1932,25 +1928,25 @@
       <c r="D21" s="35"/>
       <c r="E21" s="35"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="159">
-        <v>772332</v>
+        <v>796657</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="159"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="59" t="s">
         <v>36</v>
       </c>
@@ -1958,12 +1954,12 @@
       <c r="C24" s="59"/>
       <c r="D24" s="168">
         <f>SUM(D22:D23)</f>
-        <v>772332</v>
+        <v>796657</v>
       </c>
       <c r="E24" s="143"/>
       <c r="G24" s="22"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
@@ -1972,39 +1968,39 @@
       <c r="D25" s="159"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="29"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="159"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="159"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="169"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="186">
+      <c r="D29" s="169">
         <v>490846</v>
       </c>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="59" t="s">
         <v>36</v>
       </c>
@@ -2016,7 +2012,7 @@
       </c>
       <c r="E30" s="143"/>
     </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="30" t="s">
         <v>1</v>
       </c>
@@ -2025,11 +2021,11 @@
       <c r="D31" s="171"/>
       <c r="E31" s="144">
         <f>D24+D30</f>
-        <v>1263178</v>
+        <v>1287503</v>
       </c>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="36" t="s">
         <v>19</v>
       </c>
@@ -2038,24 +2034,24 @@
       <c r="D32" s="172"/>
       <c r="E32" s="145"/>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="188" t="s">
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="180" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="189"/>
+      <c r="B33" s="181"/>
       <c r="C33" s="54"/>
-      <c r="D33" s="182">
+      <c r="D33" s="159">
         <v>35000</v>
       </c>
       <c r="E33" s="146"/>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="188" t="s">
+    <row r="34" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="180" t="s">
         <v>109</v>
       </c>
-      <c r="B34" s="189"/>
+      <c r="B34" s="181"/>
       <c r="C34" s="54"/>
-      <c r="D34" s="185">
+      <c r="D34" s="205">
         <v>112400</v>
       </c>
       <c r="E34" s="146"/>
@@ -2063,7 +2059,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="30" t="s">
         <v>16</v>
       </c>
@@ -2075,7 +2071,7 @@
         <v>147400</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
         <v>32</v>
       </c>
@@ -2084,13 +2080,13 @@
       <c r="D36" s="174"/>
       <c r="E36" s="148"/>
     </row>
-    <row r="37" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="192" t="s">
+    <row r="37" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="184" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="193"/>
+      <c r="B37" s="185"/>
       <c r="C37" s="56"/>
-      <c r="D37" s="184">
+      <c r="D37" s="206">
         <f>26570+6696</f>
         <v>33266</v>
       </c>
@@ -2098,13 +2094,13 @@
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="196" t="s">
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="180" t="s">
         <v>95</v>
       </c>
-      <c r="B38" s="197"/>
+      <c r="B38" s="181"/>
       <c r="C38" s="56"/>
-      <c r="D38" s="183">
+      <c r="D38" s="207">
         <v>54278</v>
       </c>
       <c r="E38" s="149" t="str">
@@ -2112,7 +2108,7 @@
         <v>Debito 02/12</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="30" t="s">
         <v>2</v>
       </c>
@@ -2124,7 +2120,7 @@
         <v>87544</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
         <v>17</v>
       </c>
@@ -2133,13 +2129,13 @@
       <c r="D40" s="175"/>
       <c r="E40" s="152"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="54"/>
-      <c r="D41" s="181">
+      <c r="D41" s="208">
         <v>561889.18999999994</v>
       </c>
       <c r="E41" s="160" t="s">
@@ -2147,26 +2143,26 @@
       </c>
       <c r="G41" s="127"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="54"/>
-      <c r="D42" s="181">
+      <c r="D42" s="208">
         <v>10602.27</v>
       </c>
       <c r="E42" s="160" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="54"/>
-      <c r="D43" s="181">
+      <c r="D43" s="208">
         <v>75532.289999999994</v>
       </c>
       <c r="E43" s="160" t="str">
@@ -2175,27 +2171,27 @@
       </c>
       <c r="G43" s="142"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>101</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="180">
+      <c r="D44" s="163">
         <v>79844.990000000005</v>
       </c>
       <c r="E44" s="160" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="str">
         <f>A44</f>
         <v>Sindicatos mes de DICIEMBRE</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="180">
+      <c r="D45" s="163">
         <v>5131.7700000000004</v>
       </c>
       <c r="E45" s="161" t="str">
@@ -2203,14 +2199,14 @@
         <v>Debito 12/12</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="str">
         <f>A45</f>
         <v>Sindicatos mes de DICIEMBRE</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="180">
+      <c r="D46" s="163">
         <v>46185.919999999998</v>
       </c>
       <c r="E46" s="162" t="str">
@@ -2218,7 +2214,7 @@
         <v>Debito 12/12</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="30" t="s">
         <v>3</v>
       </c>
@@ -2230,7 +2226,7 @@
         <v>779186.43</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="36" t="s">
         <v>18</v>
       </c>
@@ -2239,59 +2235,59 @@
       <c r="D48" s="175"/>
       <c r="E48" s="152"/>
     </row>
-    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="180">
+      <c r="D49" s="163">
         <v>67167.600000000006</v>
       </c>
       <c r="E49" s="160" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B50" s="163"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="180">
+      <c r="D50" s="163">
         <v>28837.72</v>
       </c>
       <c r="E50" s="160" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="180">
+      <c r="D51" s="163">
         <v>26548.26</v>
       </c>
       <c r="E51" s="160" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="192" t="s">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="184" t="s">
         <v>77</v>
       </c>
-      <c r="B52" s="193"/>
+      <c r="B52" s="185"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="180">
+      <c r="D52" s="163">
         <v>438036.18</v>
       </c>
       <c r="E52" s="160" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="30" t="s">
         <v>4</v>
       </c>
@@ -2303,86 +2299,92 @@
         <v>560589.76</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="36"/>
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
       <c r="D54" s="173"/>
       <c r="E54" s="153"/>
     </row>
-    <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="165" t="s">
         <v>96</v>
       </c>
       <c r="B55" s="158"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="180">
+      <c r="D55" s="163">
         <v>85000</v>
       </c>
       <c r="E55" s="164" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="165" t="s">
         <v>97</v>
       </c>
       <c r="B56" s="158"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="180">
+      <c r="D56" s="163">
         <v>78000</v>
       </c>
       <c r="E56" s="164" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="165" t="s">
         <v>113</v>
       </c>
       <c r="B57" s="158"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="131">
+      <c r="D57" s="109">
         <v>600000</v>
       </c>
       <c r="E57" s="164" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="192" t="s">
+    <row r="58" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="184" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="193"/>
+      <c r="B58" s="185"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="131">
+      <c r="D58" s="109">
         <v>220000</v>
       </c>
       <c r="E58" s="164"/>
     </row>
-    <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="165" t="s">
         <v>110</v>
       </c>
       <c r="B59" s="158"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="131">
+      <c r="D59" s="109">
         <v>19726.189999999999</v>
       </c>
       <c r="E59" s="164" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="192"/>
-      <c r="B60" s="193"/>
+    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="184" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" s="185"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="109"/>
-      <c r="E60" s="164"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="193"/>
-    </row>
-    <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D60" s="109">
+        <v>85000</v>
+      </c>
+      <c r="E60" s="164" t="s">
+        <v>116</v>
+      </c>
+      <c r="I60" s="184"/>
+      <c r="J60" s="185"/>
+    </row>
+    <row r="61" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="30" t="s">
         <v>9</v>
       </c>
@@ -2391,10 +2393,10 @@
       <c r="D61" s="35"/>
       <c r="E61" s="154">
         <f>SUM(D55:D60)</f>
-        <v>1002726.19</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1087726.19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="36" t="s">
         <v>12</v>
       </c>
@@ -2403,29 +2405,30 @@
       <c r="D62" s="171"/>
       <c r="E62" s="153"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="180">
+      <c r="D63" s="163">
         <v>53000</v>
       </c>
       <c r="E63" s="155"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>91</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="180">
-        <v>56953.55</v>
+      <c r="D64" s="163">
+        <f>56953.55+12000</f>
+        <v>68953.55</v>
       </c>
       <c r="E64" s="41"/>
     </row>
-    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="53" t="s">
         <v>16</v>
       </c>
@@ -2434,17 +2437,17 @@
       <c r="D65" s="112"/>
       <c r="E65" s="106">
         <f>SUM(D63:D64)</f>
-        <v>109953.55</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>121953.55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
       <c r="D66" s="105"/>
       <c r="E66" s="113"/>
     </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="31" t="s">
         <v>51</v>
       </c>
@@ -2453,13 +2456,13 @@
       <c r="D67" s="114"/>
       <c r="E67" s="115"/>
     </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="D68" s="116"/>
       <c r="E68" s="117"/>
       <c r="F68" s="45"/>
     </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>13</v>
       </c>
@@ -2468,7 +2471,7 @@
       <c r="D69" s="118"/>
       <c r="E69" s="119">
         <f>(SUM(E27:E67))</f>
-        <v>3950577.93</v>
+        <v>4071902.93</v>
       </c>
       <c r="F69" s="142"/>
       <c r="G69" s="45"/>
@@ -2478,7 +2481,7 @@
       <c r="K69" s="127"/>
       <c r="L69" s="127"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D70" s="116"/>
       <c r="E70" s="116"/>
       <c r="H70" s="127"/>
@@ -2487,12 +2490,12 @@
       <c r="K70" s="127"/>
       <c r="L70" s="127"/>
     </row>
-    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D71" s="116"/>
       <c r="E71" s="116"/>
       <c r="H71" s="178"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
         <v>46</v>
       </c>
@@ -2501,35 +2504,35 @@
       <c r="D72" s="120"/>
       <c r="E72" s="121"/>
     </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="192"/>
-      <c r="B73" s="193"/>
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="184"/>
+      <c r="B73" s="185"/>
       <c r="C73" s="5"/>
       <c r="D73" s="131"/>
       <c r="E73" s="107"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="192"/>
-      <c r="B74" s="193"/>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="184"/>
+      <c r="B74" s="185"/>
       <c r="C74" s="5"/>
       <c r="D74" s="109"/>
       <c r="E74" s="107"/>
     </row>
-    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="188"/>
-      <c r="B75" s="189"/>
+    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="180"/>
+      <c r="B75" s="181"/>
       <c r="C75" s="5"/>
       <c r="D75" s="109"/>
       <c r="E75" s="107"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="108"/>
       <c r="B76" s="110"/>
       <c r="C76" s="5"/>
       <c r="D76" s="109"/>
       <c r="E76" s="107"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="51"/>
       <c r="B77" s="50"/>
       <c r="C77" s="50"/>
@@ -2539,9 +2542,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="31" t="s">
         <v>20</v>
       </c>
@@ -2550,8 +2553,8 @@
       <c r="D80" s="32"/>
       <c r="E80" s="104"/>
     </row>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>21</v>
       </c>
@@ -2563,26 +2566,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="102" t="s">
         <v>14</v>
       </c>
       <c r="B84" s="103">
         <f>E69</f>
-        <v>3950577.93</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>4071902.93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="102" t="s">
         <v>15</v>
       </c>
       <c r="B85" s="103">
         <f>E69-E67</f>
-        <v>3950577.93</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>4071902.93</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="102" t="s">
         <v>22</v>
       </c>
@@ -2591,7 +2594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="102" t="s">
         <v>41</v>
       </c>
@@ -2600,44 +2603,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="198"/>
-      <c r="B90" s="198"/>
-      <c r="C90" s="198"/>
-      <c r="D90" s="198"/>
-      <c r="E90" s="198"/>
-    </row>
-    <row r="91" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="198"/>
-      <c r="B91" s="198"/>
-      <c r="C91" s="198"/>
-      <c r="D91" s="198"/>
-      <c r="E91" s="198"/>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="198"/>
-      <c r="B92" s="198"/>
-      <c r="C92" s="198"/>
-      <c r="D92" s="198"/>
-      <c r="E92" s="198"/>
-    </row>
-    <row r="94" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="188"/>
+      <c r="B90" s="188"/>
+      <c r="C90" s="188"/>
+      <c r="D90" s="188"/>
+      <c r="E90" s="188"/>
+    </row>
+    <row r="91" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="188"/>
+      <c r="B91" s="188"/>
+      <c r="C91" s="188"/>
+      <c r="D91" s="188"/>
+      <c r="E91" s="188"/>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="188"/>
+      <c r="B92" s="188"/>
+      <c r="C92" s="188"/>
+      <c r="D92" s="188"/>
+      <c r="E92" s="188"/>
+    </row>
+    <row r="94" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="23" t="s">
         <v>34</v>
       </c>
       <c r="B94" s="128"/>
       <c r="C94" s="24"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="34"/>
       <c r="B95" s="61">
         <v>0</v>
       </c>
       <c r="C95" s="26"/>
     </row>
-    <row r="96" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="25" t="s">
         <v>7</v>
       </c>
@@ -2647,14 +2650,14 @@
       </c>
       <c r="C96" s="24"/>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="25"/>
       <c r="B97" s="41">
         <v>0</v>
       </c>
       <c r="C97" s="24"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="25" t="s">
         <v>42</v>
       </c>
@@ -2664,29 +2667,29 @@
       </c>
       <c r="C98" s="24"/>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="28"/>
       <c r="B99" s="49"/>
       <c r="C99" s="24"/>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="126" t="s">
         <v>47</v>
       </c>
       <c r="B100" s="49"/>
       <c r="C100" s="24"/>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="40" t="s">
         <v>23</v>
       </c>
       <c r="B101" s="49">
         <f>-B85</f>
-        <v>-3950577.93</v>
+        <v>-4071902.93</v>
       </c>
       <c r="C101" s="24"/>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="28" t="s">
         <v>24</v>
       </c>
@@ -2696,53 +2699,53 @@
       </c>
       <c r="C102" s="24"/>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B103" s="61">
         <f>SUM(B95:B102)</f>
-        <v>-450392.64999999991</v>
+        <v>-571717.64999999991</v>
       </c>
       <c r="C103" s="27"/>
       <c r="D103" s="45"/>
     </row>
-    <row r="104" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="42"/>
       <c r="C104" s="27"/>
       <c r="D104" s="45"/>
       <c r="E104" s="129"/>
       <c r="F104" s="130"/>
     </row>
-    <row r="105" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="43"/>
       <c r="C105" s="27"/>
     </row>
-    <row r="106" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="B106" s="42"/>
       <c r="C106" s="38"/>
     </row>
-    <row r="107" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="134" t="s">
         <v>88</v>
       </c>
       <c r="B107" s="135">
-        <v>220559.39390000375</v>
+        <v>-292661.08609999577</v>
       </c>
       <c r="C107" s="38"/>
       <c r="D107" s="48"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="56" t="s">
         <v>52</v>
       </c>
       <c r="B108" s="140">
         <f>-B85</f>
-        <v>-3950577.93</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-4071902.93</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="56" t="s">
         <v>53</v>
       </c>
@@ -2751,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="56" t="s">
         <v>86</v>
       </c>
@@ -2760,7 +2763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="56" t="s">
         <v>54</v>
       </c>
@@ -2769,33 +2772,33 @@
         <v>3500185.2800000003</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="138" t="s">
         <v>49</v>
       </c>
       <c r="B112" s="139">
         <f>SUM(B107:C111)</f>
-        <v>-229833.25609999616</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+        <v>-864378.73609999567</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="136"/>
       <c r="B113" s="136"/>
     </row>
-    <row r="114" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="199" t="s">
+    <row r="114" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="189" t="s">
         <v>33</v>
       </c>
-      <c r="B115" s="199"/>
-      <c r="C115" s="199"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="199"/>
-      <c r="B116" s="199"/>
-      <c r="C116" s="199"/>
-    </row>
-    <row r="117" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B115" s="189"/>
+      <c r="C115" s="189"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="189"/>
+      <c r="B116" s="189"/>
+      <c r="C116" s="189"/>
+    </row>
+    <row r="117" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="123"/>
       <c r="B117" s="37"/>
       <c r="C117" s="37">
@@ -2803,13 +2806,13 @@
       </c>
       <c r="E117" s="142"/>
     </row>
-    <row r="118" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="123"/>
       <c r="B118" s="125"/>
       <c r="C118" s="122"/>
       <c r="D118" s="142"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="46" t="s">
         <v>9</v>
       </c>
@@ -2819,36 +2822,36 @@
       </c>
       <c r="C119" s="47"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M120" s="8"/>
     </row>
-    <row r="121" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="198"/>
-      <c r="B121" s="198"/>
-      <c r="C121" s="198"/>
-      <c r="D121" s="198"/>
-      <c r="E121" s="198"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="198"/>
-      <c r="B122" s="198"/>
-      <c r="C122" s="198"/>
-      <c r="D122" s="198"/>
-      <c r="E122" s="198"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="198"/>
-      <c r="B123" s="198"/>
-      <c r="C123" s="198"/>
-      <c r="D123" s="198"/>
-      <c r="E123" s="198"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="198"/>
-      <c r="B124" s="198"/>
-      <c r="C124" s="198"/>
-      <c r="D124" s="198"/>
-      <c r="E124" s="198"/>
+    <row r="121" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="188"/>
+      <c r="B121" s="188"/>
+      <c r="C121" s="188"/>
+      <c r="D121" s="188"/>
+      <c r="E121" s="188"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="188"/>
+      <c r="B122" s="188"/>
+      <c r="C122" s="188"/>
+      <c r="D122" s="188"/>
+      <c r="E122" s="188"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="188"/>
+      <c r="B123" s="188"/>
+      <c r="C123" s="188"/>
+      <c r="D123" s="188"/>
+      <c r="E123" s="188"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="188"/>
+      <c r="B124" s="188"/>
+      <c r="C124" s="188"/>
+      <c r="D124" s="188"/>
+      <c r="E124" s="188"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -2879,44 +2882,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
     <col min="13" max="13" width="12" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="0.109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="0.140625" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
-      <c r="L1" s="200"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="190"/>
+      <c r="F1" s="190"/>
+      <c r="G1" s="190"/>
+      <c r="H1" s="190"/>
+      <c r="I1" s="190"/>
+      <c r="J1" s="190"/>
+      <c r="K1" s="190"/>
+      <c r="L1" s="190"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2941,7 +2944,7 @@
       <c r="N2" s="57"/>
       <c r="O2" s="22"/>
     </row>
-    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2957,71 +2960,71 @@
       <c r="M3" s="58"/>
       <c r="N3" s="62"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="205" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="195" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="195" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="195" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="195" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="201" t="s">
+      <c r="E4" s="191" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="205" t="s">
+      <c r="F4" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="207" t="s">
+      <c r="G4" s="197" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="201" t="s">
+      <c r="H4" s="191" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="191" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="201" t="s">
+      <c r="J4" s="191" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="210" t="s">
+      <c r="K4" s="200" t="s">
         <v>83</v>
       </c>
       <c r="L4" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="203" t="s">
+      <c r="M4" s="193" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="212" t="s">
+      <c r="N4" s="202" t="s">
         <v>37</v>
       </c>
       <c r="Q4" s="45"/>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="206"/>
-      <c r="B5" s="206"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="206"/>
-      <c r="E5" s="202"/>
-      <c r="F5" s="206"/>
-      <c r="G5" s="208"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="202"/>
-      <c r="K5" s="211"/>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="196"/>
+      <c r="B5" s="196"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="196"/>
+      <c r="E5" s="192"/>
+      <c r="F5" s="196"/>
+      <c r="G5" s="198"/>
+      <c r="H5" s="192"/>
+      <c r="I5" s="199"/>
+      <c r="J5" s="192"/>
+      <c r="K5" s="201"/>
       <c r="L5" s="63" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/01</v>
       </c>
-      <c r="M5" s="204"/>
-      <c r="N5" s="213"/>
-    </row>
-    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="194"/>
+      <c r="N5" s="203"/>
+    </row>
+    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="66">
         <v>1</v>
       </c>
@@ -3035,7 +3038,7 @@
       <c r="E6" s="76">
         <v>258261.01</v>
       </c>
-      <c r="F6" s="187">
+      <c r="F6" s="78">
         <f>E6</f>
         <v>258261.01</v>
       </c>
@@ -3074,7 +3077,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="66">
         <f>A6+1</f>
         <v>2</v>
@@ -3127,7 +3130,7 @@
       </c>
       <c r="P7" s="45"/>
     </row>
-    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="66">
         <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
@@ -3179,7 +3182,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="66">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -3194,7 +3197,7 @@
       <c r="E9" s="76">
         <v>267599.03999999998</v>
       </c>
-      <c r="F9" s="187">
+      <c r="F9" s="78">
         <f t="shared" ref="F9:F23" si="9">E9</f>
         <v>267599.03999999998</v>
       </c>
@@ -3235,7 +3238,7 @@
       </c>
       <c r="Q9" s="45"/>
     </row>
-    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="66">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -3250,7 +3253,7 @@
       <c r="E10" s="76">
         <v>647933.05000000005</v>
       </c>
-      <c r="F10" s="187">
+      <c r="F10" s="78">
         <f>E10</f>
         <v>647933.05000000005</v>
       </c>
@@ -3291,7 +3294,7 @@
       </c>
       <c r="Q10" s="45"/>
     </row>
-    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="66">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -3306,7 +3309,7 @@
       <c r="E11" s="76">
         <v>182597.06</v>
       </c>
-      <c r="F11" s="187">
+      <c r="F11" s="78">
         <f t="shared" si="9"/>
         <v>182597.06</v>
       </c>
@@ -3346,7 +3349,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="66">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -3398,7 +3401,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="66">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -3413,7 +3416,7 @@
       <c r="E13" s="76">
         <v>218885.08</v>
       </c>
-      <c r="F13" s="187">
+      <c r="F13" s="78">
         <f>E13</f>
         <v>218885.08</v>
       </c>
@@ -3456,7 +3459,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="66">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -3471,7 +3474,7 @@
       <c r="E14" s="76">
         <v>296093.09000000003</v>
       </c>
-      <c r="F14" s="187">
+      <c r="F14" s="78">
         <f t="shared" si="9"/>
         <v>296093.09000000003</v>
       </c>
@@ -3511,7 +3514,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="66">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -3526,7 +3529,7 @@
       <c r="E15" s="76">
         <v>189160.1</v>
       </c>
-      <c r="F15" s="187">
+      <c r="F15" s="78">
         <f>E15+RESUMEN!D58</f>
         <v>409160.1</v>
       </c>
@@ -3566,7 +3569,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="66">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -3581,7 +3584,7 @@
       <c r="E16" s="76">
         <v>217341.11</v>
       </c>
-      <c r="F16" s="187">
+      <c r="F16" s="78">
         <f t="shared" si="9"/>
         <v>217341.11</v>
       </c>
@@ -3621,7 +3624,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="66">
         <f t="shared" si="7"/>
         <v>12</v>
@@ -3636,7 +3639,7 @@
       <c r="E17" s="76">
         <v>214252.12</v>
       </c>
-      <c r="F17" s="187">
+      <c r="F17" s="78">
         <f t="shared" si="9"/>
         <v>214252.12</v>
       </c>
@@ -3676,7 +3679,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="66">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -3691,7 +3694,7 @@
       <c r="E18" s="76">
         <v>426961.13</v>
       </c>
-      <c r="F18" s="187">
+      <c r="F18" s="78">
         <f>E18</f>
         <v>426961.13</v>
       </c>
@@ -3731,7 +3734,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="66">
         <f t="shared" si="7"/>
         <v>14</v>
@@ -3783,7 +3786,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="66">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -3798,7 +3801,7 @@
       <c r="E20" s="76">
         <v>69487.149999999994</v>
       </c>
-      <c r="F20" s="187">
+      <c r="F20" s="78">
         <v>71572.149999999994</v>
       </c>
       <c r="G20" s="79">
@@ -3837,7 +3840,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="66">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -3852,7 +3855,7 @@
       <c r="E21" s="76">
         <v>124305.16</v>
       </c>
-      <c r="F21" s="187">
+      <c r="F21" s="78">
         <f>E21</f>
         <v>124305.16</v>
       </c>
@@ -3893,7 +3896,7 @@
       </c>
       <c r="Q21" s="44"/>
     </row>
-    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="66">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -3947,7 +3950,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="66">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -3962,7 +3965,7 @@
       <c r="E23" s="76">
         <v>165225.18</v>
       </c>
-      <c r="F23" s="187">
+      <c r="F23" s="78">
         <f t="shared" si="9"/>
         <v>165225.18</v>
       </c>
@@ -4002,7 +4005,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="66"/>
       <c r="B24" s="66"/>
       <c r="C24" s="67"/>
@@ -4022,7 +4025,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="86"/>
       <c r="B25" s="66"/>
       <c r="C25" s="67"/>
@@ -4039,7 +4042,7 @@
       <c r="N25" s="85"/>
       <c r="O25" s="45"/>
     </row>
-    <row r="26" spans="1:17" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="86"/>
       <c r="B26" s="68"/>
       <c r="C26" s="67"/>
@@ -4056,7 +4059,7 @@
       <c r="N26" s="85"/>
       <c r="O26" s="45"/>
     </row>
-    <row r="27" spans="1:17" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="87"/>
       <c r="B27" s="66"/>
       <c r="C27" s="67"/>
@@ -4073,7 +4076,7 @@
       <c r="N27" s="85"/>
       <c r="O27" s="45"/>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="66"/>
       <c r="B28" s="93"/>
       <c r="C28" s="93"/>
@@ -4090,7 +4093,7 @@
       <c r="N28" s="96"/>
       <c r="O28" s="45"/>
     </row>
-    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="97"/>
       <c r="B29" s="98"/>
       <c r="C29" s="98"/>
@@ -4139,91 +4142,91 @@
         <v>5877513.71</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="52"/>
       <c r="C30" s="52"/>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="198" t="str">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="188" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="198"/>
-      <c r="D32" s="198"/>
-      <c r="E32" s="198"/>
-      <c r="F32" s="198"/>
-      <c r="G32" s="198"/>
-      <c r="H32" s="198"/>
-      <c r="I32" s="198"/>
-      <c r="J32" s="198"/>
-      <c r="K32" s="198"/>
-      <c r="L32" s="198"/>
-    </row>
-    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="198"/>
-      <c r="C33" s="198"/>
-      <c r="D33" s="198"/>
-      <c r="E33" s="198"/>
-      <c r="F33" s="198"/>
-      <c r="G33" s="198"/>
-      <c r="H33" s="198"/>
-      <c r="I33" s="198"/>
-      <c r="J33" s="198"/>
-      <c r="K33" s="198"/>
-      <c r="L33" s="198"/>
-    </row>
-    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="198"/>
-      <c r="C34" s="198"/>
-      <c r="D34" s="198"/>
-      <c r="E34" s="198"/>
-      <c r="F34" s="198"/>
-      <c r="G34" s="198"/>
-      <c r="H34" s="198"/>
-      <c r="I34" s="198"/>
-      <c r="J34" s="198"/>
-      <c r="K34" s="198"/>
-      <c r="L34" s="198"/>
-    </row>
-    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="198"/>
-      <c r="C35" s="198"/>
-      <c r="D35" s="198"/>
-      <c r="E35" s="198"/>
-      <c r="F35" s="198"/>
-      <c r="G35" s="198"/>
-      <c r="H35" s="198"/>
-      <c r="I35" s="198"/>
-      <c r="J35" s="198"/>
-      <c r="K35" s="198"/>
-      <c r="L35" s="198"/>
-    </row>
-    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="198"/>
-      <c r="C36" s="198"/>
-      <c r="D36" s="198"/>
-      <c r="E36" s="198"/>
-      <c r="F36" s="198"/>
-      <c r="G36" s="198"/>
-      <c r="H36" s="198"/>
-      <c r="I36" s="198"/>
-      <c r="J36" s="198"/>
-      <c r="K36" s="198"/>
-      <c r="L36" s="198"/>
-    </row>
-    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="198"/>
-      <c r="C37" s="198"/>
-      <c r="D37" s="198"/>
-      <c r="E37" s="198"/>
-      <c r="F37" s="198"/>
-      <c r="G37" s="198"/>
-      <c r="H37" s="198"/>
-      <c r="I37" s="198"/>
-      <c r="J37" s="198"/>
-      <c r="K37" s="198"/>
-      <c r="L37" s="198"/>
+      <c r="C32" s="188"/>
+      <c r="D32" s="188"/>
+      <c r="E32" s="188"/>
+      <c r="F32" s="188"/>
+      <c r="G32" s="188"/>
+      <c r="H32" s="188"/>
+      <c r="I32" s="188"/>
+      <c r="J32" s="188"/>
+      <c r="K32" s="188"/>
+      <c r="L32" s="188"/>
+    </row>
+    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="188"/>
+      <c r="C33" s="188"/>
+      <c r="D33" s="188"/>
+      <c r="E33" s="188"/>
+      <c r="F33" s="188"/>
+      <c r="G33" s="188"/>
+      <c r="H33" s="188"/>
+      <c r="I33" s="188"/>
+      <c r="J33" s="188"/>
+      <c r="K33" s="188"/>
+      <c r="L33" s="188"/>
+    </row>
+    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="188"/>
+      <c r="C34" s="188"/>
+      <c r="D34" s="188"/>
+      <c r="E34" s="188"/>
+      <c r="F34" s="188"/>
+      <c r="G34" s="188"/>
+      <c r="H34" s="188"/>
+      <c r="I34" s="188"/>
+      <c r="J34" s="188"/>
+      <c r="K34" s="188"/>
+      <c r="L34" s="188"/>
+    </row>
+    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="188"/>
+      <c r="C35" s="188"/>
+      <c r="D35" s="188"/>
+      <c r="E35" s="188"/>
+      <c r="F35" s="188"/>
+      <c r="G35" s="188"/>
+      <c r="H35" s="188"/>
+      <c r="I35" s="188"/>
+      <c r="J35" s="188"/>
+      <c r="K35" s="188"/>
+      <c r="L35" s="188"/>
+    </row>
+    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="188"/>
+      <c r="C36" s="188"/>
+      <c r="D36" s="188"/>
+      <c r="E36" s="188"/>
+      <c r="F36" s="188"/>
+      <c r="G36" s="188"/>
+      <c r="H36" s="188"/>
+      <c r="I36" s="188"/>
+      <c r="J36" s="188"/>
+      <c r="K36" s="188"/>
+      <c r="L36" s="188"/>
+    </row>
+    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="188"/>
+      <c r="C37" s="188"/>
+      <c r="D37" s="188"/>
+      <c r="E37" s="188"/>
+      <c r="F37" s="188"/>
+      <c r="G37" s="188"/>
+      <c r="H37" s="188"/>
+      <c r="I37" s="188"/>
+      <c r="J37" s="188"/>
+      <c r="K37" s="188"/>
+      <c r="L37" s="188"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -4251,9 +4254,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="C5:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C5" s="179" t="s">
         <v>89</v>
       </c>
